--- a/assets/constructions/examples/ctd_mcs.xlsx
+++ b/assets/constructions/examples/ctd_mcs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,75 +664,94 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GYF95160</t>
+          <t>R215.34C12040-DS12K 1640</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GYF95</t>
+          <t>CoroMill® Plura R215.3хС..40-DS..K</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>js12</t>
-        </is>
-      </c>
+          <t>PMKS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>14</v>
+        <v>11.2</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L2" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="P2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>HB-12</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>5</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>HB-16</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>WORKPIECE</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>h6</t>
@@ -740,59 +759,79 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>PM60</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr"/>
+          <t>1640</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>AlCrN</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t xml:space="preserve">PVD TIALN </t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>DIN 6527 K</t>
+        </is>
+      </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB2" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.117</v>
+      </c>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2018 - YG1 - OnlyOne</t>
+          <t xml:space="preserve"> 08.1 </t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AT2" t="b">
@@ -800,22 +839,33 @@
       </c>
       <c r="AU2" t="b">
         <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>49N908003.. UNCOATED</t>
+          <t>MB265-20.0A3X200B-WJ30CA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>49N9</t>
+          <t>MB265</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -826,38 +876,38 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>d11</t>
+          <t>h9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>7.5</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -868,44 +918,48 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>h6</t>
+          <t>h5</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>UNCOATED</t>
+          <t>WJ30CA</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>CrN</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>PWZ-NORM XL</t>
+        </is>
+      </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -914,7 +968,9 @@
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+      <c r="AN3" t="n">
+        <v>4</v>
+      </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
@@ -922,7 +978,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2020/End Mills Widia Hanita RU</t>
+          <t>2017/Общий каталог WALTER 2017</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -934,23 +990,34 @@
         <v>0</v>
       </c>
       <c r="AU3" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CSRARBD1000R200</t>
+          <t>49N920007.. UNCOATED</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MITSUBISHI</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CSRARB</t>
+          <t>49N9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -959,34 +1026,40 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>d11</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18</v>
+      </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -995,8 +1068,16 @@
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>UNCOATED</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
@@ -1011,22 +1092,22 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>9.4</v>
+        <v>18.7</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1043,7 +1124,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2020 / Mitsubishi Website</t>
+          <t>2020/End Mills Widia Hanita RU</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1056,22 +1137,33 @@
       </c>
       <c r="AU4" t="b">
         <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>49N92001R7JT UNCOATED</t>
+          <t>MB265-16.0A3X200A-WJ30UU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49N9</t>
+          <t>MB265</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1082,38 +1174,38 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>d11</t>
+          <t>h9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
         <v>20</v>
       </c>
-      <c r="J5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>38</v>
-      </c>
       <c r="M5" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HA-16</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1124,12 +1216,12 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>h6</t>
+          <t>h5</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>UNCOATED</t>
+          <t>WJ30UU</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1138,30 +1230,34 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>PWZ-NORM XL</t>
+        </is>
+      </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB5" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>18.7</v>
+        <v>15.2</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
@@ -1170,7 +1266,9 @@
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>4</v>
+      </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
@@ -1178,7 +1276,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2020/End Mills Widia Hanita RU</t>
+          <t>2017/Общий каталог WALTER 2017</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1190,69 +1288,72 @@
         <v>0</v>
       </c>
       <c r="AU5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GYF95100</t>
+          <t>R216.36-16045IYK32K 1640</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GYF95</t>
+          <t>CoroMillⓇ Plura solid carbide end mill for roughing with chip breaker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>js12</t>
-        </is>
-      </c>
+          <t>PMKS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>HB-10</t>
+          <t>SAFE-LOCK:16</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1268,16 +1369,24 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>PM60</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
+          <t>1640</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>AlCrN</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+          <t>PVD TICN</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>DIN 6527 L</t>
+        </is>
+      </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
@@ -1285,42 +1394,54 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AB6" t="n">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>15.2</v>
+      </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+          <t>SAFE-LOCK</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.307</v>
+      </c>
       <c r="AQ6" t="n">
         <v>0</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2018 - YG1 - OnlyOne</t>
+          <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AT6" t="b">
@@ -1328,6 +1449,17 @@
       </c>
       <c r="AU6" t="b">
         <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
       </c>
     </row>
   </sheetData>
